--- a/informed_consent_forms/004_dental_hipaa_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/004_dental_hipaa_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -735,8 +735,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -764,12 +764,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'patient_information'}</t>
+          <t>patient_information</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Patient Information'}</t>
+          <t>Patient Information</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'name'}</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Name'}</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'phone_number'}</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Phone Number'}</t>
+          <t>Phone Number</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'anesthesia'}</t>
+          <t>anesthesia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Anesthesia'}</t>
+          <t>Anesthesia</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'biopsy'}</t>
+          <t>biopsy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Biopsy'}</t>
+          <t>Biopsy</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cast'}</t>
+          <t>cast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cast'}</t>
+          <t>Cast</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'cleaning'}</t>
+          <t>cleaning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Cleaning'}</t>
+          <t>Cleaning</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'consultation'}</t>
+          <t>consultation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Consultation'}</t>
+          <t>Consultation</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'diagnostic_imaging'}</t>
+          <t>diagnostic_imaging</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Diagnostic Imaging'}</t>
+          <t>Diagnostic Imaging</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'extraction'}</t>
+          <t>extraction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Extraction'}</t>
+          <t>Extraction</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'fluoride'}</t>
+          <t>fluoride</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Fluoride'}</t>
+          <t>Fluoride</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'general_anesthesia'}</t>
+          <t>general_anesthesia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'General Anesthesia'}</t>
+          <t>General Anesthesia</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'oral_surgery'}</t>
+          <t>oral_surgery</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Oral Surgery'}</t>
+          <t>Oral Surgery</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'restorative'}</t>
+          <t>restorative</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Restorative'}</t>
+          <t>Restorative</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'chronic_disease'}</t>
+          <t>chronic_disease</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Chronic Disease'}</t>
+          <t>Chronic Disease</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'medical_condition_1'}</t>
+          <t>medical_condition_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Medical Condition 1'}</t>
+          <t>Medical Condition 1</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'medical_condition_2'}</t>
+          <t>medical_condition_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Medical Condition 2'}</t>
+          <t>Medical Condition 2</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
